--- a/output/育児・介護休業規程_いいかいご.xlsx
+++ b/output/育児・介護休業規程_いいかいご.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -591,69 +591,75 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>3　「子の看護休暇」：小学校就学前の子の看護のために取得できる休暇をいう。</t>
+          <t>3　「子の看護等休暇」：小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のために取得できる休暇をいう。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>5　「出生時育児休業」：子の出生後8週間以内に4週間（28日）まで取得できる休業をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>4　「介護休暇」：要介護状態にある家族の介護や通院付添のために取得できる休暇をいう。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="8" customHeight="1"/>
-    <row r="41" ht="8" customHeight="1">
-      <c r="A41" s="7" t="inlineStr"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-    </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>第2章　育児休業</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>（育児休業の取得要件）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>第4条　従業員は、1歳に満たない子を養育する場合、会社に申し出ることにより育児休業を取得できる。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>2　配偶者が常態として子を養育できる場合等、法令で育児休業が認められない場合は除く。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業の期間）</t>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2　育児休業は、子1人につき原則2回まで分割して取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>3　労使協定により、次の者を育児休業の対象から除外することがある。（1）継続雇用期間が1年未満の者　（2）申出の日から1年以内に雇用関係が終了することが明らかな者　（3）1週間の所定労働日数が2日以下の者</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
+          <t>4　有期雇用の従業員は、子が1歳6か月に達する日までに労働契約が満了し更新されないことが明らかでない場合に取得できる。</t>
         </is>
       </c>
     </row>
@@ -661,14 +667,14 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>（育児休業の申出）</t>
+          <t>（育児休業の期間）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
         </is>
       </c>
     </row>
@@ -676,341 +682,527 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>（育児休業中の処遇）</t>
+          <t>（育児休業の申出）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="8" customHeight="1">
-      <c r="A58" s="7" t="inlineStr"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-    </row>
-    <row r="59" ht="10" customHeight="1"/>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>第3章　介護休業</t>
-        </is>
-      </c>
-    </row>
+          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>（出生時育児休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>第6条の2　従業員は、子の出生後8週間以内に、4週間（28日）を限度として、2回まで分割して出生時育児休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2　出生時育児休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>（介護休業の取得要件）</t>
+          <t>（育児休業中の処遇）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="8" customHeight="1">
+      <c r="A65" s="7" t="inlineStr"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>第3章　介護休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>（介護休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
           <t>第8条　従業員は、要介護状態にある家族を介護する場合、会社に申し出ることにより介護休業を取得できる。</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="8" customHeight="1"/>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>（介護休業の期間）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>第9条　介護休業は、対象家族1人につき通算93日まで取得できる。分割して3回まで分けて取得することができる。</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="8" customHeight="1"/>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>（介護休業の申出）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>第10条　介護休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに、所定の書式により会社へ申し出なければならない。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="8" customHeight="1"/>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>（介護休業中の処遇）</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>第11条　介護休業中は無給とする。ただし、雇用保険法に基づき介護休業給付金の受給が可能である。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="8" customHeight="1"/>
-    <row r="73" ht="8" customHeight="1">
-      <c r="A73" s="7" t="inlineStr"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-    </row>
-    <row r="74" ht="10" customHeight="1"/>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>第4章　子の看護休暇・介護休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>（子の看護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、小学校就学前の子が病気やけがをした場合、看護のため年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>2　子の看護休暇は、1日または半日単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
     <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>（介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>2　介護休暇は、1日または半日単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="8" customHeight="1">
-      <c r="A84" s="7" t="inlineStr"/>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="10" customHeight="1"/>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>第5章　復職・不利益取扱い禁止</t>
-        </is>
-      </c>
-    </row>
+    <row r="80" ht="8" customHeight="1">
+      <c r="A80" s="7" t="inlineStr"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+    </row>
+    <row r="81" ht="10" customHeight="1"/>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>第4章　子の看護等休暇・介護休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のため、年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2　子の看護等休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>（復職）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="48" customHeight="1">
+          <t>（介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>第15条　会社は、従業員が育児休業・介護休業・子の看護休暇・介護休暇を取得したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="8" customHeight="1">
-      <c r="A93" s="7" t="inlineStr"/>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
-    </row>
-    <row r="94" ht="10" customHeight="1"/>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>第6章　雑則</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>（制度の周知）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="8" customHeight="1"/>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>（個人情報保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="32" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="8" customHeight="1"/>
-    <row r="102" ht="8" customHeight="1">
-      <c r="A102" s="7" t="inlineStr"/>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="10" customHeight="1"/>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
+          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2　介護休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="8" customHeight="1">
+      <c r="A91" s="7" t="inlineStr"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+    </row>
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>第4章の2　働き方の制限・措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>（所定外労働の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>第13条の2　小学校就学前の子を養育する従業員、または要介護状態にある家族を介護する従業員が請求した場合、事業の正常な運営を妨げる場合を除き、所定労働時間を超えて労働させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>（時間外労働・深夜業の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>第13条の3　前条の従業員が請求した場合、時間外労働は1か月24時間、1年150時間を超えないものとし、深夜（午後10時から午前5時まで）に労働させない。ただし、法令に定める除外者はこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>（短時間勤務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>第13条の4　3歳に満たない子を養育する従業員、または要介護状態にある家族を介護する従業員は、申し出により、所定労働時間を1日6時間とする短時間勤務を利用できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>（柔軟な働き方を実現するための措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>第13条の5　3歳から小学校就学前の子を養育する従業員に対し、会社は次の措置を講じ、従業員はいずれか1つを選択して利用できる。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+          <t>1　始業・終業時刻の変更（時差出勤）</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
+          <t>2　養育両立支援休暇（年10日、時間単位で取得可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>（個別周知・意向確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>第13条の6　会社は、従業員から本人または配偶者の妊娠・出産の申出があったとき、及び子が3歳になる前の適切な時期に、育児休業等の制度を個別に周知し、取得や働き方の意向を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、従業員から家族の介護に直面した旨の申出があったとき、介護休業等の制度を個別に周知し、意向を確認する。また、40歳に達した従業員に対し、介護両立支援制度の情報を提供する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>（ハラスメントの防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>第13条の7　会社は、妊娠・出産、育児休業・介護休業等の利用に関する言動により従業員の就業環境が害されることのないよう、相談体制の整備その他必要な措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="8" customHeight="1">
+      <c r="A115" s="7" t="inlineStr"/>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+    </row>
+    <row r="116" ht="10" customHeight="1"/>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>第5章　復職・不利益取扱い禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>（復職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>第15条　会社は、従業員が育児休業・出生時育児休業・介護休業・子の看護等休暇・介護休暇その他本規程の制度を利用したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="7" t="inlineStr"/>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>第6章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>（制度の周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="8" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>（個人情報保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="7" t="inlineStr"/>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
           <t>2　本規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="84">
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A96:E96"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A117:E117"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
